--- a/processed_ruby_restored_xlsx/sc223_瑠璃５：バレエレオタード.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc223_瑠璃５：バレエレオタード.ss.xlsx
@@ -532,7 +532,8 @@
       <c r="B5" s="1" t="inlineStr">
         <is>
           <t>So they sent a ballet teacher to Makishima, and they
-decided to hold lessons in the Gakuen's Assembly Hall.</t>
+decided to hold lessons in the Gakuen's Assembly
+Hall.</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1331,8 +1332,8 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>「Oh my... Oji-sama, your face just softened, you know？
-Ufufu！」</t>
+          <t>「Oh my... Oji-sama, your face just softened, you
+know？ Ufufu！」</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1531,8 +1532,8 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>As I answered instantly, Rurichiyo-chan started taking
-off her clothes.</t>
+          <t>As I answered instantly, Rurichiyo-chan started
+taking off her clothes.</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1593,8 +1594,8 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>「Ta-da！ I thought you'd say you wanted to see it... so
-I put it on underneath！」</t>
+          <t>「Ta-da！ I thought you'd say you wanted to see it...
+so I put it on underneath！」</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1639,7 +1640,8 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>In that moment my excitement shot straight to the top.</t>
+          <t>In that moment my excitement shot straight to the
+top.</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1822,8 +1824,8 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>At that time I was so carried away I couldn't see what
-was around me.</t>
+          <t>At that time I was so carried away I couldn't see
+what was around me.</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1838,8 +1840,8 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>There was no way I could notice Rurichiyo-chan inching
-closer and closer.</t>
+          <t>There was no way I could notice Rurichiyo-chan
+inching closer and closer.</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2158,7 +2160,8 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>I didn't miss the tiny voice Rurichiyo-chan whispered.</t>
+          <t>I didn't miss the tiny voice Rurichiyo-chan
+whispered.</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2403,8 +2406,8 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>She flinched and gave a small jump when I touched her,
-but she didn't try to resist.</t>
+          <t>She flinched and gave a small jump when I touched
+her, but she didn't try to resist.</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2755,7 +2758,8 @@
       <c r="B150" s="1" t="inlineStr">
         <is>
           <t>You could clearly see the way her back arched —
-precisely because the leotard clung to her so closely.</t>
+precisely because the leotard clung to her so
+closely.</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2831,8 +2835,8 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>「Good girl, good girl... Rurichiyo-chan, you're a good
-girl, aren't you?」</t>
+          <t>「Good girl, good girl... Rurichiyo-chan, you're a
+good girl, aren't you?」</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2937,7 +2941,8 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>I lightly patted the fluffy skirt, as if soothing her.</t>
+          <t>I lightly patted the fluffy skirt, as if soothing
+her.</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3104,7 +3109,8 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>I cup Rurichiyo-chan’s rounded butt, squeeze！ squeeze！</t>
+          <t>I cup Rurichiyo-chan’s rounded butt, squeeze！
+squeeze！</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3135,8 +3141,8 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan seems to tense up, and the leotard digs
-into her butt.</t>
+          <t>Rurichiyo-chan seems to tense up, and the leotard
+digs into her butt.</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3348,7 +3354,8 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>「These legs of yours are so cute… I really love them.」</t>
+          <t>「These legs of yours are so cute… I really love
+them.」</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3872,8 +3879,8 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan got angry because she genuinely thought
-so.</t>
+          <t>Rurichiyo-chan got angry because she genuinely
+thought so.</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -4361,7 +4368,8 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>She wraps her arms around my neck and clings on tight.</t>
+          <t>She wraps her arms around my neck and clings on
+tight.</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4927,7 +4935,8 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>「I love the Rurichiyo-chan who lets me spoil her too—」</t>
+          <t>「I love the Rurichiyo-chan who lets me spoil her
+too—」</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -5380,8 +5389,8 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>Again, when I really started moving my hips, the flesh
-of her pussy began trembling in time with me.</t>
+          <t>Again, when I really started moving my hips, the
+flesh of her pussy began trembling in time with me.</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5763,7 +5772,8 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>For this moment only, it feels as if time has stopped.</t>
+          <t>For this moment only, it feels as if time has
+stopped.</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -5946,8 +5956,8 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t>Remembering the feel of her bared chest, its smallness
-pressed its softness against me.</t>
+          <t>Remembering the feel of her bared chest, its
+smallness pressed its softness against me.</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -6160,8 +6170,8 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t>With each exchange it feels better and better, my body
-filling with pleasure.</t>
+          <t>With each exchange it feels better and better, my
+body filling with pleasure.</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -6654,8 +6664,8 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t>They keep sucking on each other’s lips without getting
-bored.</t>
+          <t>They keep sucking on each other’s lips without
+getting bored.</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -6930,7 +6940,8 @@
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan writhes her tongue up and down, lewdly.</t>
+          <t>Rurichiyo-chan writhes her tongue up and down,
+lewdly.</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -7083,7 +7094,8 @@
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t>「Nn, ah... nffuu！ Oji-saama...？ Nn... there, there...」</t>
+          <t>「Nn, ah... nffuu！ Oji-saama...？ Nn... there,
+there...」</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -7327,8 +7339,8 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>You asked me to let you hear my voice, and yet I don't
-want to stop kissing you.</t>
+          <t>You asked me to let you hear my voice, and yet I
+don't want to stop kissing you.</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7664,8 +7676,9 @@
       </c>
       <c r="B471" s="1" t="inlineStr">
         <is>
-          <t>With a squelching sound as they stayed stuck together,
-even her juices were spilling out in abundance.</t>
+          <t>With a squelching sound as they stayed stuck
+together, even her juices were spilling out in
+abundance.</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -7680,8 +7693,8 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t>I start to feel like it would be okay to have my penis
-melted away inside Rurichiyo-chan.</t>
+          <t>I start to feel like it would be okay to have my
+penis melted away inside Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -8091,8 +8104,8 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>The more she begs, the more I can't help it—I trail my
-fingers along her spine with a shiver.</t>
+          <t>The more she begs, the more I can't help it—I trail
+my fingers along her spine with a shiver.</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8229,7 +8242,8 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan looks at me with a yearning expression.</t>
+          <t>Rurichiyo-chan looks at me with a yearning
+expression.</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -8304,7 +8318,8 @@
       </c>
       <c r="B513" s="1" t="inlineStr">
         <is>
-          <t>「Haahm！ Chumu, chu！ Chupuu...！ Aaah！ Ahf, ahfu！ Nnn~！」</t>
+          <t>「Haahm！ Chumu, chu！ Chupuu...！ Aaah！ Ahf, ahfu！
+Nnn~！」</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -8705,7 +8720,8 @@
       </c>
       <c r="B539" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama！ Oji-sama... chu！ Chuu...！ Chupa, chu！ Chu！」</t>
+          <t>「Oji-sama！ Oji-sama... chu！ Chuu...！ Chupa, chu！
+Chu！」</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -9135,8 +9151,8 @@
       </c>
       <c r="B567" s="1" t="inlineStr">
         <is>
-          <t>Still thinking of Rurichiyo-chan, I hold her tight and
-press their bodies even closer together.</t>
+          <t>Still thinking of Rurichiyo-chan, I hold her tight
+and press their bodies even closer together.</t>
         </is>
       </c>
       <c r="C567" t="n">

--- a/processed_ruby_restored_xlsx/sc223_瑠璃５：バレエレオタード.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc223_瑠璃５：バレエレオタード.ss.xlsx
@@ -4063,7 +4063,7 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>「I wonder if it's no good...？」</t>
+          <t>I wonder if it's no good...？</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>「Are you going to end up hating me？」</t>
+          <t>Are you going to end up hating me？</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4783,8 +4783,8 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>「That's outrageous！ Actually, I feel like I'm just
-getting hornier and hornier...」</t>
+          <t>That's outrageous！ Actually, I feel like I'm just
+getting hornier and hornier...</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4859,8 +4859,8 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>I got aroused by her earnestness and cuteness, and my
-penis trembled.</t>
+          <t>He got aroused by her earnestness and cuteness, and
+his penis trembled.</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>I kept moving my hips like that….</t>
+          <t>He kept moving his hips like that….</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>Saying that, I started thrusting properly.</t>
+          <t>Saying that, he started thrusting properly.</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>I was curtly refused, and I groaned out of
+          <t>He was curtly refused, and I groaned out of
 embarrassment. My hips stopped moving too.</t>
         </is>
       </c>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu！　Chu-chu！　Chuuuuu...！」</t>
+          <t>Ufufu！　Chu-chu！　Chuuuuu...！</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>「Ahh... fufu！ Chuu...」</t>
+          <t>Ahh... fufu！ Chuu...</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B437" s="1" t="inlineStr">
         <is>
-          <t>「There, there… nn, ufufu！ Fufu！ …nn！ Fuu, fwwaaaaa……」</t>
+          <t>There, there… nn, ufufu！ Fufu！ …nn！ Fuu, fwwaaaaa……</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>「nchu—...chu, chupa！」</t>
+          <t>nchu—...chu, chupa！</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -8150,7 +8150,8 @@
       </c>
       <c r="B502" s="1" t="inlineStr">
         <is>
-          <t>I squeeze the penis tight~ like it's begging for cum.</t>
+          <t>He squeezes the penis tight~ like it's begging for
+cum.</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -8428,7 +8429,7 @@
       </c>
       <c r="B520" s="1" t="inlineStr">
         <is>
-          <t>「Nnna, aa... ha, haaa... u！ Uwa！ Ah... ah！ Ah！ Ah！」</t>
+          <t>Nnna, aa... ha, haaa... u！ Uwa！ Ah... ah！ Ah！ Ah！</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -8458,7 +8459,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>「Ah, Rurichiyo-chan！ Rurichiyo-chaaan！」</t>
+          <t>Ah, Rurichiyo-chan！ Rurichiyo-chaaan！</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8505,8 +8506,8 @@
       </c>
       <c r="B525" s="1" t="inlineStr">
         <is>
-          <t>「Chuu... puhaa！ Oji-sama, nn！ It's reaching me... ah！
-Aa, ah！」</t>
+          <t>Chuu... puhaa！ Oji-sama, nn！ It's reaching me... ah！
+Aa, ah！</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -8536,7 +8537,7 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>「What's reaching you？ Tell me... chu！」</t>
+          <t>What's reaching you？ Tell me... chu！</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8566,8 +8567,8 @@
       </c>
       <c r="B529" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaaa... chu chu, ha！ Oji-sama's... o-oh, my penis
-is...」</t>
+          <t>Fuwaaa... chu chu, ha！ Oji-sama's... o-oh, his penis
+is...</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -8597,7 +8598,7 @@
       </c>
       <c r="B531" s="1" t="inlineStr">
         <is>
-          <t>「Fuchuu...！ The penis, nn？ Fufu！」</t>
+          <t>Fuchuu...！ The penis, nn？ Fufu！</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -8627,7 +8628,7 @@
       </c>
       <c r="B533" s="1" t="inlineStr">
         <is>
-          <t>「The penis... nnaaaah！」</t>
+          <t>The penis... nnaaaah！</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -8690,7 +8691,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>「Fufuu, nn！ Rurichiyo-chaaaan！ Hah！」</t>
+          <t>Fufuu, nn！ Rurichiyo-chaaaan！ Hah！</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -8720,8 +8721,7 @@
       </c>
       <c r="B539" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama！ Oji-sama... chu！ Chuu...！ Chupa, chu！
-Chu！」</t>
+          <t>Oji-sama！ Oji-sama... chu！ Chuu...！ Chupa, chu！ Chu！</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="B543" s="1" t="inlineStr">
         <is>
-          <t>「Haf！ It's good...！ Nn！ Chuchuuu... nnn~~！ Chuppaa！」</t>
+          <t>Haf！ It's good...！ Nn！ Chuchuuu... nnn~~！ Chuppaa！</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -8813,8 +8813,8 @@
       </c>
       <c r="B545" s="1" t="inlineStr">
         <is>
-          <t>「Uu, aha！ Chuu... nn！ It feels so good,
-Rurichiyo-chan, aaah！」</t>
+          <t>Uu, aha！ Chuu... nn！ It feels so good,
+Rurichiyo-chan, aaah！</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="B566" s="1" t="inlineStr">
         <is>
-          <t>I begin to ejaculate, and my body starts trembling
+          <t>He begins to ejaculate, and his body starts trembling
 again.</t>
         </is>
       </c>
@@ -9151,8 +9151,8 @@
       </c>
       <c r="B567" s="1" t="inlineStr">
         <is>
-          <t>Still thinking of Rurichiyo-chan, I hold her tight
-and press their bodies even closer together.</t>
+          <t>Still thinking of Rurichiyo-chan, he holds her tight
+and presses their bodies even closer together.</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -9698,8 +9698,8 @@
       </c>
       <c r="B603" s="1" t="inlineStr">
         <is>
-          <t>「Hey, you lot！ Stop yapping away forever and get home
-already！」</t>
+          <t>Hey, you lot！ Stop yapping away forever and get home
+already！</t>
         </is>
       </c>
       <c r="C603" t="n">
